--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/EMBREAGEM PRIMÁRIA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/EMBREAGEM PRIMÁRIA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EMBREAGEM PRIMARIA COMPLETA JAPAN PCX160 20231106501</t>
+          <t>EMBREAGEM PRIMARIA COMPLETA WW3  PCX160 20231106501</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EMBREAGEM PRIMARIA COMPLETA JAPAN NMAX160 2017 A 2020 1212269</t>
+          <t>EMBREAGEM PRIMARIA COMPLETA WW3  NMAX160 2017 A 2020 1212269</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EMBREAGEM PRIMARIA COMPLETA JAPAN ADV150 2021 1106503</t>
+          <t>EMBREAGEM PRIMARIA COMPLETA WW3  ADV150 2021 1106503</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EMBREAGEM PRIMARIA COMPLETA JAPAN NMAX160 2021 A 2024 1212274</t>
+          <t>EMBREAGEM PRIMARIA COMPLETA WW3  NMAX160 2021 A 2024 1212274</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -583,27 +583,6 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>79008253842961</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>EMBREAGEM SECUNDARIA COMPLETA TMAC LEAD 110 2009 A 2015 TC1129</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/EMBREAGEM PRIMÁRIA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/EMBREAGEM PRIMÁRIA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,17 +524,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TRANSMISSAO PRIMARIA COMPLETA TRILHA PCX150 2014 A 2015</t>
+          <t>EMBREAGEM PRIMARIA COMPLETA TRILHA PCX150 2014 A 2015</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>366</t>
         </is>
       </c>
     </row>
@@ -574,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TRANSMISSAO PRIMARIA COMPLETA MHX NEO125 2017 A 2023</t>
+          <t>EMBREAGEM PRIMARIA COMPLETA MHX NEO125 2017 A 2023</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -582,7 +552,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7899468090431</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMBREAGEM PRIMARIA COMPLETA MHX NMAX160 2017 A 2020</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
